--- a/wwwroot/AdminRequestFileUpload/Cheque_Print_v1.xlsx.xlsx
+++ b/wwwroot/AdminRequestFileUpload/Cheque_Print_v1.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TharakaJayam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587820D3-4F8F-4BEC-A4E5-0C4FE3152D53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499AE8CB-31CD-49F3-BAF6-7A96CD26C1D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="18960" windowHeight="8940" xr2:uid="{0DD34650-9568-41C2-9258-39CAA0E6F6CF}"/>
   </bookViews>
@@ -414,7 +414,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>46265</v>
+        <v>46247</v>
       </c>
       <c r="C2" s="2">
         <v>10000</v>
